--- a/generated-papers/Tags_NDA_APJ_GAT_Mock_5.xlsx
+++ b/generated-papers/Tags_NDA_APJ_GAT_Mock_5.xlsx
@@ -2594,10 +2594,10 @@
         <v>QSRP</v>
       </c>
       <c r="J47" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="K47" t="str">
-        <v>After the traveller asks for an inn (S1), the peasant clarifies (P), the traveller confirms (S), and the peasant gives directions (R) before the closing thanks. Matches option A.</v>
+        <v>Dialogue order: the traveller asks whether the peasant can help (S1); the peasant replies 'Yes' (Q); the peasant then asks whether he wants an inn to spend the night in (P); the traveller replies 'Yes' (S); the peasant gives the directions (R); the traveller thanks him (S6). Sequence QPSR. Matches option B.</v>
       </c>
       <c r="L47" t="str">
         <v>Moderate</v>
